--- a/docs/TAPP_EPMA_filled-noInterp.xlsx
+++ b/docs/TAPP_EPMA_filled-noInterp.xlsx
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>CDIF-geochem schema path</t>
+          <t>schema path</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">

--- a/docs/TAPP_EPMA_filled-noInterp.xlsx
+++ b/docs/TAPP_EPMA_filled-noInterp.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="729" yWindow="737" windowWidth="18300" windowHeight="9952" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="94" yWindow="2263" windowWidth="21849" windowHeight="9951" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
@@ -1096,6 +1096,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1103,8 +1111,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1113,12 +1119,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1415,11 +1415,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.69140625" defaultRowHeight="12.45"/>
   <cols>
     <col width="28.69140625" customWidth="1" style="4" min="1" max="1"/>
-    <col width="33" customWidth="1" style="199" min="2" max="2"/>
-    <col width="14.69140625" bestFit="1" customWidth="1" style="199" min="3" max="3"/>
-    <col width="14.69140625" customWidth="1" style="199" min="4" max="4"/>
-    <col width="16.84375" customWidth="1" style="199" min="5" max="5"/>
-    <col width="26.15234375" customWidth="1" style="200" min="6" max="6"/>
+    <col width="33" customWidth="1" style="198" min="2" max="2"/>
+    <col width="14.69140625" bestFit="1" customWidth="1" style="198" min="3" max="3"/>
+    <col width="14.69140625" customWidth="1" style="198" min="4" max="4"/>
+    <col width="16.84375" customWidth="1" style="198" min="5" max="5"/>
+    <col width="26.15234375" customWidth="1" style="199" min="6" max="6"/>
     <col width="10.84375" customWidth="1" style="4" min="7" max="7"/>
     <col width="28.3046875" customWidth="1" min="8" max="8"/>
     <col width="37.15234375" customWidth="1" min="9" max="9"/>
@@ -1436,8 +1436,8 @@
     <col width="37" customWidth="1" min="24" max="24"/>
     <col width="28.3046875" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="28"/>
-    <col width="12.69140625" customWidth="1" style="4" min="29" max="29"/>
-    <col width="12.69140625" customWidth="1" style="4" min="30" max="16384"/>
+    <col width="12.69140625" customWidth="1" style="4" min="29" max="30"/>
+    <col width="12.69140625" customWidth="1" style="4" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -1600,7 +1600,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="198" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>1. Method Identification</t>
         </is>
@@ -2472,16 +2472,16 @@
       <c r="AB11" s="122" t="n"/>
     </row>
     <row r="12" customFormat="1" s="70">
-      <c r="A12" s="196" t="inlineStr">
+      <c r="A12" s="200" t="inlineStr">
         <is>
           <t>2. Samples</t>
         </is>
       </c>
-      <c r="B12" s="197" t="n"/>
-      <c r="C12" s="197" t="n"/>
-      <c r="D12" s="197" t="n"/>
-      <c r="E12" s="197" t="n"/>
-      <c r="F12" s="197" t="n"/>
+      <c r="B12" s="201" t="n"/>
+      <c r="C12" s="201" t="n"/>
+      <c r="D12" s="201" t="n"/>
+      <c r="E12" s="201" t="n"/>
+      <c r="F12" s="201" t="n"/>
       <c r="G12" s="69" t="n"/>
       <c r="H12" s="157" t="n"/>
       <c r="I12" s="69" t="n"/>
@@ -2811,16 +2811,16 @@
       <c r="AB15" s="122" t="n"/>
     </row>
     <row r="16" customFormat="1" s="70">
-      <c r="A16" s="201" t="inlineStr">
+      <c r="A16" s="203" t="inlineStr">
         <is>
           <t>3. Instrument &amp; Software</t>
         </is>
       </c>
-      <c r="B16" s="197" t="n"/>
-      <c r="C16" s="197" t="n"/>
-      <c r="D16" s="197" t="n"/>
-      <c r="E16" s="197" t="n"/>
-      <c r="F16" s="197" t="n"/>
+      <c r="B16" s="201" t="n"/>
+      <c r="C16" s="201" t="n"/>
+      <c r="D16" s="201" t="n"/>
+      <c r="E16" s="201" t="n"/>
+      <c r="F16" s="201" t="n"/>
       <c r="G16" s="69" t="n"/>
       <c r="H16" s="157" t="n"/>
       <c r="I16" s="69" t="n"/>
@@ -3211,7 +3211,7 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D20" s="205" t="inlineStr">
+      <c r="D20" s="196" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
@@ -3308,7 +3308,7 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D21" s="205" t="inlineStr">
+      <c r="D21" s="196" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
@@ -3594,16 +3594,16 @@
       <c r="AB24" s="122" t="n"/>
     </row>
     <row r="25" customFormat="1" s="70">
-      <c r="A25" s="202" t="inlineStr">
+      <c r="A25" s="204" t="inlineStr">
         <is>
           <t>4. Measurement Information</t>
         </is>
       </c>
-      <c r="B25" s="197" t="n"/>
-      <c r="C25" s="197" t="n"/>
-      <c r="D25" s="197" t="n"/>
-      <c r="E25" s="197" t="n"/>
-      <c r="F25" s="197" t="n"/>
+      <c r="B25" s="201" t="n"/>
+      <c r="C25" s="201" t="n"/>
+      <c r="D25" s="201" t="n"/>
+      <c r="E25" s="201" t="n"/>
+      <c r="F25" s="201" t="n"/>
       <c r="G25" s="69" t="n"/>
       <c r="H25" s="157" t="n"/>
       <c r="I25" s="69" t="n"/>
@@ -3643,7 +3643,7 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D26" s="205" t="inlineStr">
+      <c r="D26" s="196" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
@@ -3782,7 +3782,7 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D27" s="205" t="inlineStr">
+      <c r="D27" s="196" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
@@ -3922,7 +3922,7 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D28" s="205" t="inlineStr">
+      <c r="D28" s="196" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="I29" s="69" t="inlineStr">
         <is>
-          <t>$.ada:methodParameters[]</t>
+          <t>$MethodDefinition.schema:additionalProperty['Beam Raster Dimensions'].schema:value</t>
         </is>
       </c>
       <c r="J29" s="69" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="I30" s="69" t="inlineStr">
         <is>
-          <t>$.ada:methodParameters[].schema:description</t>
+          <t>$MethodDefinition.schema:additionalProperty['Beam Damage Minimization'].schema:value</t>
         </is>
       </c>
       <c r="J30" s="69" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="I31" s="110" t="inlineStr">
         <is>
-          <t>$.ada:methodParameters[].schema:description</t>
+          <t>$MethodDefinition.schema:additionalProperty['Drift Correction'].schema:value</t>
         </is>
       </c>
       <c r="J31" s="110" t="inlineStr">
@@ -4359,7 +4359,7 @@
     <row r="33" ht="77.25" customHeight="1" thickBot="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Default Beam Current</t>
+          <t>Beam Current</t>
         </is>
       </c>
       <c r="B33" s="36" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D33" s="38" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E33" s="36" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D35" s="40" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E35" s="39" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D36" s="40" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E36" s="39" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D37" s="37" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E37" s="36" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="D39" s="40" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E39" s="39" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E41" s="36" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D42" s="38" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E42" s="36" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="D43" s="40" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E43" s="39" t="inlineStr">
@@ -5435,7 +5435,7 @@
       <c r="AB44" s="115" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="203" t="inlineStr">
+      <c r="A45" s="205" t="inlineStr">
         <is>
           <t>5. Data Processing</t>
         </is>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>$.ada:methodParameters[]</t>
+          <t>$MethodDefinition.schema:additionalProperty['Halogen Correction on Oxygen'].schema:value</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D49" s="42" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E49" s="41" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>$.ada:methodParameters[]</t>
+          <t>$MethodDefinition.schema:additionalProperty['EDS Spectral Processing Type'].schema:value</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D53" s="48" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E53" s="47" t="inlineStr">
@@ -6399,7 +6399,7 @@
       <c r="AB57" s="138" t="n"/>
     </row>
     <row r="58" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A58" s="204" t="inlineStr">
+      <c r="A58" s="197" t="inlineStr">
         <is>
           <t>6. Quality Control &amp; Uncertainty</t>
         </is>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D60" s="52" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E60" s="51" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D62" s="54" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E62" s="53" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D64" s="54" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E64" s="53" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D66" s="54" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E66" s="53" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D67" s="54" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E67" s="53" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D68" s="54" t="inlineStr">
         <is>
-          <t>editable</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E68" s="53" t="inlineStr">
